--- a/data/trans_orig/IP22D4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D4_2023-Estudios-trans_orig.xlsx
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33274</t>
+          <t>33362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62145</t>
+          <t>61505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66678</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47786</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>52863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94100</t>
+          <t>94306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>100353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D4_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5658</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33535</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31829</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29373</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26197</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>28988</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25654</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>29862</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35945</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>33362</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36860</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>87</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>62523</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61505</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66689</t>
+          <t>63843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>874</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2552</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2765</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,74 +1632,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8287</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5160</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>56,39%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9177</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6984</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>71,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9315</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6726</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>68,24%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10754</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>59,07%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>24</t>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>541</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,102 +2093,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>41616</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>37864</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>51507</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>47283</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>52863</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>88504</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>84107</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>90584</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>96,69%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>98249</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>94306</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>100353</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -2314,107 +2314,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
